--- a/tools/importer/reports/import-news-v1.report.xlsx
+++ b/tools/importer/reports/import-news-v1.report.xlsx
@@ -73,7 +73,7 @@
     <t>news</t>
   </si>
   <si>
-    <t>2026-09-07T07:46:22.106Z</t>
+    <t>2026-09-07T10:27:10.543Z</t>
   </si>
   <si>
     <t>USTA Foundation, OFFLINE by Aerie® and the Aerie Real Foundation™ partner to empower next generation of women in tennis</t>

--- a/tools/importer/reports/import-news-v1.report.xlsx
+++ b/tools/importer/reports/import-news-v1.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="398">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,12 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>errorStack</t>
+  </si>
+  <si>
     <t>path</t>
   </si>
   <si>
@@ -43,6 +49,9 @@
     <t>["hero-banner","columns-stats","columns-statement","columns-feature","columns-feature","cards-support"]</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>en/home</t>
   </si>
   <si>
@@ -61,6 +70,947 @@
     <t>https://www.ustafoundation.com/en/home.html</t>
   </si>
   <si>
+    <t>en/home/news/2023-njtl-essay-contest-winners.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","social","reactions","table×1"]</t>
+  </si>
+  <si>
+    <t>en/home/news/2023-njtl-essay-contest-winners</t>
+  </si>
+  <si>
+    <t>news</t>
+  </si>
+  <si>
+    <t>2026-09-07T16:26:50.132Z</t>
+  </si>
+  <si>
+    <t>2023 NJTL Essay Contest Winners</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/2023-njtl-essay-contest-winners.html</t>
+  </si>
+  <si>
+    <t>en/home/news/2026-usta-foundation-opening-night-gala-provides-young-people-wi.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","social","columns-media×1"]</t>
+  </si>
+  <si>
+    <t>en/home/news/2026-usta-foundation-opening-night-gala-provides-young-people-wi</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:09:08.361Z</t>
+  </si>
+  <si>
+    <t>2026 USTA Foundation Opening Night Gala provides young people with opportunities to unlock their excellence</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/2026-usta-foundation-opening-night-gala-provides-young-people-wi.html</t>
+  </si>
+  <si>
+    <t>en/home/news/black-history-month-2026-community-impact-hub-leader-john-borde.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","social","reactions","columns-media×2"]</t>
+  </si>
+  <si>
+    <t>en/home/news/black-history-month-2026-community-impact-hub-leader-john-borde</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:09:14.937Z</t>
+  </si>
+  <si>
+    <t>Black History Month 2026: Community Impact Hub leader John Borden reflects on tennis as an ‘unexpected anchor’</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/black-history-month-2026--community-impact-hub-leader-john-borde.html</t>
+  </si>
+  <si>
+    <t>en/home/news/carol-ngounoue-runner-up-wimbledon-event.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","quote-tweet×2","social","reactions","tweet-split×1","columns-media×1"]</t>
+  </si>
+  <si>
+    <t>en/home/news/carol-ngounoue-runner-up-wimbledon-event</t>
+  </si>
+  <si>
+    <t>2026-09-07T19:02:34.848Z</t>
+  </si>
+  <si>
+    <t>Carel Ngounoue finishes runner-up at inaugural 14-and-under Wimbledon event</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/carol-ngounoue-runner-up-wimbledon-event.html</t>
+  </si>
+  <si>
+    <t>en/home/news/chris-evert-honored-espn-sports-humanitarian-awards.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","quote-tweet×1","social","reactions","tweet-split×1","columns-media×1"]</t>
+  </si>
+  <si>
+    <t>en/home/news/chris-evert-honored-espn-sports-humanitarian-awards</t>
+  </si>
+  <si>
+    <t>2026-09-07T19:02:41.839Z</t>
+  </si>
+  <si>
+    <t>Chris Evert to be honored by ESPN at 2022 Sports Humanitarian Awards</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/chris-evert-honored-espn-sports-humanitarian-awards.html</t>
+  </si>
+  <si>
+    <t>en/home/news/chris-evert-honored-espys-usta-foundation-work.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","quote-tweet×1","social","reactions","columns-media×1"]</t>
+  </si>
+  <si>
+    <t>en/home/news/chris-evert-honored-espys-usta-foundation-work</t>
+  </si>
+  <si>
+    <t>2026-09-07T19:02:48.536Z</t>
+  </si>
+  <si>
+    <t>Watch: Chris Evert honored at ESPYs for USTA Foundation work</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/chris-evert-honored-espys-usta-foundation-work.html</t>
+  </si>
+  <si>
+    <t>en/home/news/chris-evert-usta-foundation-much-more.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","social","reactions","columns-media×1"]</t>
+  </si>
+  <si>
+    <t>en/home/news/chris-evert-usta-foundation-much-more</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:09:38.793Z</t>
+  </si>
+  <si>
+    <t>Chris Evert: 'The USTA Foundation is about so much more than hitting a ball'</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/chris-evert-usta-foundation-much-more.html</t>
+  </si>
+  <si>
+    <t>en/home/news/clervie-ngounoue-first-junior-grand-slam-australia.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/clervie-ngounoue-first-junior-grand-slam-australia</t>
+  </si>
+  <si>
+    <t>2026-09-07T19:02:55.274Z</t>
+  </si>
+  <si>
+    <t>Clervie Ngounoue reaches first junior Grand Slam final in Australia</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/clervie-ngounoue-first-junior-grand-slam-australia.html</t>
+  </si>
+  <si>
+    <t>en/home/news/clervie-ngounoue-wins-first-junior-grand-slam-australian-open.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/clervie-ngounoue-wins-first-junior-grand-slam-australian-open</t>
+  </si>
+  <si>
+    <t>2026-09-07T19:03:02.544Z</t>
+  </si>
+  <si>
+    <t>Clervie Ngounoue wins first junior Grand Slam at Australian Open</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/clervie-ngounoue-wins-first-junior-grand-slam-australian-open.html</t>
+  </si>
+  <si>
+    <t>en/home/news/daymond-john-and-matt-ebert-share-wisdom-with-usta-foundation-s.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/daymond-john-and-matt-ebert-share-wisdom-with-usta-foundation-s</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:08:54.123Z</t>
+  </si>
+  <si>
+    <t>Daymond John and Matt Ebert share wisdom with USTA Foundation students during 2025 US Open</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/-daymond-john-and-matt-ebert-share-wisdom-with-usta-foundation-s.html</t>
+  </si>
+  <si>
+    <t>en/home/news/delray-beach-youth-tennis-foundation-athletes-hit-the-court-with.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","social","reactions","columns-media×3"]</t>
+  </si>
+  <si>
+    <t>en/home/news/delray-beach-youth-tennis-foundation-athletes-hit-the-court-with</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:09:58.713Z</t>
+  </si>
+  <si>
+    <t>Delray Beach Youth Tennis Foundation athletes hit the court with Frances Tiafoe</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/delray-beach-youth-tennis-foundation-athletes-hit-the-court-with.html</t>
+  </si>
+  <si>
+    <t>en/home/news/desert-smash-brings-together-hollywood-and-pro-tennis-to-benefit.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/desert-smash-brings-together-hollywood-and-pro-tennis-to-benefit</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:10:04.940Z</t>
+  </si>
+  <si>
+    <t>Desert Smash brings together Hollywood and pro tennis to benefit USTA Foundation</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/desert-smash-brings-together-hollywood-and-pro-tennis-to-benefit.html</t>
+  </si>
+  <si>
+    <t>en/home/news/espn-chris-mckendry-supports-usta-foundation.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/espn-chris-mckendry-supports-usta-foundation</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:10:11.512Z</t>
+  </si>
+  <si>
+    <t>ESPN's Chris McKendry explains why she supports the USTA Foundation</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/espn-chris-mckendry-supports-usta-foundation.html</t>
+  </si>
+  <si>
+    <t>en/home/news/evert-speaks-on-rally-to-rebuild.html.report.json</t>
+  </si>
+  <si>
+    <t>page.evaluate: Target page, context or browser has been closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.evaluate: Target page, context or browser has been closed
+    at processUrl (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:639:16)
+    at async main (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:954:22)</t>
+  </si>
+  <si>
+    <t>en/home/news/evert-speaks-on-rally-to-rebuild.html</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:08:09.871Z</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/evert-speaks-on-rally-to-rebuild.html</t>
+  </si>
+  <si>
+    <t>en/home/news/evert-speaks-on-rally-to-rebuild.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/evert-speaks-on-rally-to-rebuild</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:10:18.612Z</t>
+  </si>
+  <si>
+    <t>Evert speaks on 'Rally to Rebuild' in NY, LA: 'We want to get these kids back playing'</t>
+  </si>
+  <si>
+    <t>en/home/news/excellence-program-alumna-robin-montgomery-reaches-first-wta-sem.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/excellence-program-alumna-robin-montgomery-reaches-first-wta-sem</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:10:24.773Z</t>
+  </si>
+  <si>
+    <t>Excellence Program alumna Robin Montgomery reaches first WTA semifinal</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/excellence-program-alumna-robin-montgomery-reaches-first-wta-sem.html</t>
+  </si>
+  <si>
+    <t>en/home/news/fashion-icon-anna-wintour-honored-with-usta-foundation-paver-on.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/fashion-icon-anna-wintour-honored-with-usta-foundation-paver-on</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:10:31.926Z</t>
+  </si>
+  <si>
+    <t>Fashion icon Anna Wintour honored with USTA Foundation paver on US Open's Avenue of Aces</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/fashion-icon-anna-wintour-honored-with-usta-foundation-paver-on-.html</t>
+  </si>
+  <si>
+    <t>en/home/news/frances-tiafoe-awards-njtl-alumnus-with-college-scholarship.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/frances-tiafoe-awards-njtl-alumnus-with-college-scholarship</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:10:38.258Z</t>
+  </si>
+  <si>
+    <t>Frances Tiafoe awards NJTL alumnus with $30,000 college scholarship</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/frances-tiafoe-awards-njtl-alumnus-with-college-scholarship.html</t>
+  </si>
+  <si>
+    <t>en/home/news/frances-tiafoe-fund-surpasses-1-million-raised.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/frances-tiafoe-fund-surpasses-1-million-raised</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:10:43.425Z</t>
+  </si>
+  <si>
+    <t>Frances Tiafoe Fund surpasses $1 million raised</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/frances-tiafoe-fund-surpasses--1-million-raised.html</t>
+  </si>
+  <si>
+    <t>en/home/news/frances-tiafoe-holds-clinic-for-youth-from-houston-tennis-associ.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/frances-tiafoe-holds-clinic-for-youth-from-houston-tennis-associ</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:10:49.312Z</t>
+  </si>
+  <si>
+    <t>Frances Tiafoe holds clinic for youth from Houston Tennis Association</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/frances-tiafoe-holds-clinic-for-youth-from-houston-tennis-associ.html</t>
+  </si>
+  <si>
+    <t>en/home/news/frances-tiafoe-presents-check-to-jtcc.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/frances-tiafoe-presents-check-to-jtcc</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:10:55.640Z</t>
+  </si>
+  <si>
+    <t>Frances Tiafoe presents $50,000 check to JTCC from Frances Tiafoe Fund</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/frances-tiafoe-presents-check-to-jtcc.html</t>
+  </si>
+  <si>
+    <t>en/home/news/how-the-usta-foundation-and-realize-the-dream-are-set-to-inspire.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/how-the-usta-foundation-and-realize-the-dream-are-set-to-inspire</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:11:02.584Z</t>
+  </si>
+  <si>
+    <t>How the USTA Foundation and Realize the Dream are set to inspire a new generation in service and leadership</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/how-the-usta-foundation-and-realize-the-dream-are-set-to-inspire.html</t>
+  </si>
+  <si>
+    <t>en/home/news/inaugural-usta-foundation-impact-conference.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/inaugural-usta-foundation-impact-conference</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:11:09.717Z</t>
+  </si>
+  <si>
+    <t>Inaugural USTA Foundation Impact Conference invigorates and inspires NJTL leadership</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/inaugural-usta-foundation-impact-conference.html</t>
+  </si>
+  <si>
+    <t>en/home/news/james-blake-30th-anniversary-usta-foundation.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/james-blake-30th-anniversary-usta-foundation</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:11:16.889Z</t>
+  </si>
+  <si>
+    <t>'Close to my heart': James Blake celebrates 30th anniversary of USTA Foundation</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/james-blake-30th-anniversary-usta-foundation.html</t>
+  </si>
+  <si>
+    <t>en/home/news/jinjie-ling-dwight-f-davis-memorial-scholarship.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/jinjie-ling-dwight-f-davis-memorial-scholarship</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:11:22.990Z</t>
+  </si>
+  <si>
+    <t>From the tennis courts of Houston to Duke University: Catching up with Jinjie Ling</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/jinjie-ling-dwight-f-davis-memorial-scholarship.html</t>
+  </si>
+  <si>
+    <t>en/home/news/kathleen-wu-usta-foundation-president.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/kathleen-wu-usta-foundation-president</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:11:28.776Z</t>
+  </si>
+  <si>
+    <t>Kathleen Wu announced as next USTA Foundation President</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/kathleen-wu-usta-foundation-president.html</t>
+  </si>
+  <si>
+    <t>en/home/news/kimmelman-sport-education-complex-los-angeles.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/kimmelman-sport-education-complex-los-angeles</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:11:35.048Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation and other partners commit to Kimmelman sport and education complex in Los Angeles</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/kimmelman-sport-education-complex-los-angeles.html</t>
+  </si>
+  <si>
+    <t>en/home/news/kings-county-tennis-league-nominated-for-laureus-sport-for-good.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/kings-county-tennis-league-nominated-for-laureus-sport-for-good</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:11:40.540Z</t>
+  </si>
+  <si>
+    <t>Kings County Tennis League nominated for Laureus Sport for Good Award</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/kings-county-tennis-league-nominated-for-laureus-sport-for-good-.html</t>
+  </si>
+  <si>
+    <t>en/home/news/kyrgios-sock-njtl-clinic-laver-cup-boston.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/kyrgios-sock-njtl-clinic-laver-cup-boston</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:11:48.709Z</t>
+  </si>
+  <si>
+    <t>Nick Kyrgios and Jack Sock participate in NJTL clinic at Laver Cup in Boston</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/kyrgios-sock-njtl-clinic-laver-cup-boston.html</t>
+  </si>
+  <si>
+    <t>en/home/news/laver-cup-community-legacy-project-celebrates-court-unveiling-at.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/laver-cup-community-legacy-project-celebrates-court-unveiling-at</t>
+  </si>
+  <si>
+    <t>2026-09-07T14:26:59.025Z</t>
+  </si>
+  <si>
+    <t>Laver Cup Community Legacy Project celebrates court unveiling at John McLaren Park</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/laver-cup-community-legacy-project-celebrates-court-unveiling-at.html</t>
+  </si>
+  <si>
+    <t>en/home/news/laver-cup-launches-2025-san-francisco-community-legacy-project-w.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","reactions","columns-media×1"]</t>
+  </si>
+  <si>
+    <t>en/home/news/laver-cup-launches-2025-san-francisco-community-legacy-project-w</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:11:55.719Z</t>
+  </si>
+  <si>
+    <t>Laver Cup launches 2025 San Francisco Community Legacy Project with USTA Foundation</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/laver-cup-launches-2025-san-francisco-community-legacy-project-w.html</t>
+  </si>
+  <si>
+    <t>en/home/news/leylah-fernandez-partners-with-usta-socal-and-bgcmla-for-youth-c.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/leylah-fernandez-partners-with-usta-socal-and-bgcmla-for-youth-c</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:12:02.345Z</t>
+  </si>
+  <si>
+    <t>Leylah Fernandez partners with USTA SoCal and BGCMLA for youth clinic</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/leylah-fernandez-partners-with-usta-socal-and-bgcmla-for-youth-c.html</t>
+  </si>
+  <si>
+    <t>en/home/news/mackenzie-mcdonald-celebrates-the-launch-of-the-usta-foundation.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/mackenzie-mcdonald-celebrates-the-launch-of-the-usta-foundation</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:12:15.708Z</t>
+  </si>
+  <si>
+    <t>Mackenzie McDonald celebrates the launch of the USTA Foundation's Mackie McDonald College Fund</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/mackenzie-mcdonald-celebrates-the-launch-of-the-usta-foundation-.html</t>
+  </si>
+  <si>
+    <t>en/home/news/mackenzie-mcdonald-i-m-making-it-my-mission-to-help-open-the-s.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/mackenzie-mcdonald-i-m-making-it-my-mission-to-help-open-the-s</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:12:09.038Z</t>
+  </si>
+  <si>
+    <t>Mackenzie McDonald: 'I'm making it my mission to help open the same doors for the next generation.'</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/mackenzie-mcdonald---i-m-making-it-my-mission-to-help-open-the-s.html</t>
+  </si>
+  <si>
+    <t>en/home/news/mississippi-njtl-family-biz-builder.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/mississippi-njtl-family-biz-builder</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:12:23.043Z</t>
+  </si>
+  <si>
+    <t>Mississippi NJTL Family Biz Builder featured in Tennis magazine</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/mississippi-njtl-family-biz-builder.html</t>
+  </si>
+  <si>
+    <t>en/home/news/newport-njtl-honor-chris-evert.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/newport-njtl-honor-chris-evert</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:12:30.053Z</t>
+  </si>
+  <si>
+    <t>Home of Newport NJTL named in honor of Chris Evert</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/newport-njtl-honor-chris-evert.html</t>
+  </si>
+  <si>
+    <t>en/home/news/ngounoue-excellence-team-junior-french-open.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/ngounoue-excellence-team-junior-french-open</t>
+  </si>
+  <si>
+    <t>2026-09-07T19:03:11.452Z</t>
+  </si>
+  <si>
+    <t>Montgomery, Ngounoue represent Excellence Team at junior French Open</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/ngounoue-excellence-team-junior-french-open.html</t>
+  </si>
+  <si>
+    <t>en/home/news/njtl-ace-jabeiro-brown.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/njtl-ace-jabeiro-brown</t>
+  </si>
+  <si>
+    <t>2026-09-07T16:09:08.458Z</t>
+  </si>
+  <si>
+    <t>From New York to UCF: Catching up with NJTL ace Jabeiro Brown</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/njtl-ace-jabeiro-brown.html</t>
+  </si>
+  <si>
+    <t>en/home/news/njtl-essay-contest-winners-2024-open.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","social","reactions"]</t>
+  </si>
+  <si>
+    <t>en/home/news/njtl-essay-contest-winners-2024-open</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:12:35.410Z</t>
+  </si>
+  <si>
+    <t>NJTL Essay Contest winners celebrated during 2024 US Open</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/njtl-essay-contest-winners-2024-open.html</t>
+  </si>
+  <si>
+    <t>en/home/news/njtl-essay-grant-recipients-2020.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/njtl-essay-grant-recipients-2020</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:12:42.735Z</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/njtl-essay-grant-recipients-2020.html</t>
+  </si>
+  <si>
+    <t>en/home/news/njtl-student-athlete-ata-national-championships.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/njtl-student-athlete-ata-national-championships</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:12:49.254Z</t>
+  </si>
+  <si>
+    <t>NJTL student-athletes shine at ATA National Championships</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/njtl-student-athlete-ata-national-championships.html</t>
+  </si>
+  <si>
+    <t>en/home/news/njtl-student-athletes-white-house-visit.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/njtl-student-athletes-white-house-visit</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:12:56.034Z</t>
+  </si>
+  <si>
+    <t>NJTL student-athletes enjoy once-in-a-lifetime White House visit</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/njtl-student-athletes-white-house-visit.html</t>
+  </si>
+  <si>
+    <t>en/home/news/novo-nordisk-donnelly-scholarship-winners-meet-billie-jean-king.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/novo-nordisk-donnelly-scholarship-winners-meet-billie-jean-king</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:13:03.040Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation Novo Nordisk Donnelly Scholarship winners meet Billie Jean King</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/novo-nordisk-donnelly-scholarship-winners-meet-billie-jean-king.html</t>
+  </si>
+  <si>
+    <t>en/home/news/robin-montgomery-investing-in-game.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/robin-montgomery-investing-in-game</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:13:09.743Z</t>
+  </si>
+  <si>
+    <t>Rising stock: Robin Montgomery investing in her game</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/robin-montgomery-investing-in-game.html</t>
+  </si>
+  <si>
+    <t>en/home/news/robin-montgomery-wimbledon-debut.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/robin-montgomery-wimbledon-debut</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:13:17.395Z</t>
+  </si>
+  <si>
+    <t>Excellence Team alumna Robin Montgomery makes Wimbledon debut, earns first Grand Slam main-draw win</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/robin-montgomery-wimbledon-debut.html</t>
+  </si>
+  <si>
+    <t>en/home/news/six-student-athletes-awarded-first-grants-frances-tiafoe-fund.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","social","reactions","video-embed×1","columns-media×1"]</t>
+  </si>
+  <si>
+    <t>en/home/news/six-student-athletes-awarded-first-grants-frances-tiafoe-fund</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:13:23.320Z</t>
+  </si>
+  <si>
+    <t>Six student-athletes awarded first-ever grants from the Frances Tiafoe Fund</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/six-student-athletes-awarded-first-grants-frances-tiafoe-fund.html</t>
+  </si>
+  <si>
+    <t>en/home/news/sloane-stephens-honored-by-sports-business-journal.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/sloane-stephens-honored-by-sports-business-journal</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:13:29.365Z</t>
+  </si>
+  <si>
+    <t>Sloane Stephens-founded NJTL honored by Sports Business Journal</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/sloane-stephens-honored-by-sports-business-journal.html</t>
+  </si>
+  <si>
+    <t>en/home/news/tennis-has-been-my-vehicle-to-serve-sloane-stephens-shares-he.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/tennis-has-been-my-vehicle-to-serve-sloane-stephens-shares-he</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:09:00.957Z</t>
+  </si>
+  <si>
+    <t>'Tennis has been my vehicle to serve': Sloane Stephens shares her love for community and philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/-tennis-has-been-my-vehicle-to-serve---sloane-stephens-shares-he.html</t>
+  </si>
+  <si>
+    <t>en/home/news/tiafoe-houston-youth-clinic.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/tiafoe-houston-youth-clinic</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:13:37.090Z</t>
+  </si>
+  <si>
+    <t>Frances Tiafoe joins Houston youth for clinic in support of Frances Tiafoe Fund</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/tiafoe-houston-youth-clinic.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-and-reginald-f-lewis-foundation-partner-to-empo.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-and-reginald-f-lewis-foundation-partner-to-empo</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:13:49.436Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation and The Reginald F. Lewis Foundation partner to empower future leaders and honor outstanding mentors</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-and-reginald-f--lewis-foundation-partner-to-empo.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-and-yonex-team-up-to-transform-communities-and-e.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-and-yonex-team-up-to-transform-communities-and-e</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:13:55.712Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation and Yonex team up to transform communities and empower the next generation of leaders</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-and-yonex-team-up-to-transform-communities-and-e.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-announces-chris-evert-chair.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-announces-chris-evert-chair</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:14:01.895Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation announces Chris Evert as Chair of the Board of Directors</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-announces-chris-evert-chair.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-announces-new-advisory-board-members.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-announces-new-advisory-board-members</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:14:08.528Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation announces new Advisory Board members</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-announces-new-advisory-board-members.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-announces-sloane-stephens-as-recipient-of-servin.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-announces-sloane-stephens-as-recipient-of-servin</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:14:14.428Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation announces Sloane Stephens as recipient of Serving Up Dreams Award</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-announces-sloane-stephens-as-recipient-of-servin.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-celebrates-2026-njtl-essay-contest-winners-at-us.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-celebrates-2026-njtl-essay-contest-winners-at-us</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:14:20.641Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation celebrates 2026 NJTL essay contest winners at US Open Fan Week experience presented by Deloitte</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-celebrates-2026-njtl-essay-contest-winners-at-us.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-chairperson-chris-evert-announces-cancer-free.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-chairperson-chris-evert-announces-cancer-free</t>
+  </si>
+  <si>
+    <t>2026-09-07T19:03:18.435Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation chairperson Chris Evert announces she's cancer free</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-chairperson-chris-evert-announces-cancer-free.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-chris-evert-honored-itf-commitment-award.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-chris-evert-honored-itf-commitment-award</t>
+  </si>
+  <si>
+    <t>2026-09-07T19:03:24.854Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation chairperson Chris Evert honored with ITF Commitment Award at Billie Jean King Cup</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-chris-evert-honored-itf-commitment-award.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-exceeds-goal-rally-to-rebuild-campaign.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-exceeds-goal-rally-to-rebuild-campaign</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:14:39.241Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation exceeds goal of 'Rally to Rebuild' campaign</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-exceeds-goal-rally-to-rebuild-campaign.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-launches-community-impact-hub-initiative.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","reactions","video-embed×1"]</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-launches-community-impact-hub-initiative</t>
+  </si>
+  <si>
+    <t>2026-09-07T14:01:09.347Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation launches Community Impact Hub initiative</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-launches-community-impact-hub-initiative.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-launches-williams-family-excellence-program-at-2.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-launches-williams-family-excellence-program-at-2</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:14:46.097Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation launches Williams Family Excellence Program at 2025 US Open</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-launches-williams-family-excellence-program-at-2.html</t>
+  </si>
+  <si>
     <t>en/home/news/usta-foundation-offline-by-aerie-and-the-aerie-real-foundatio.report.json</t>
   </si>
   <si>
@@ -70,9 +1020,6 @@
     <t>en/home/news/usta-foundation-offline-by-aerie-and-the-aerie-real-foundatio</t>
   </si>
   <si>
-    <t>news</t>
-  </si>
-  <si>
     <t>2026-09-07T10:27:10.543Z</t>
   </si>
   <si>
@@ -80,6 +1027,186 @@
   </si>
   <si>
     <t>https://www.ustafoundation.com/en/home/news/usta-foundation--offline-by-aerie---and-the-aerie-real-foundatio.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-partners-with-chase-to-award-over-250-000-to-he.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-partners-with-chase-to-award-over-250-000-to-he</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:14:54.711Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation partners with Chase to award over $250,000 to help support young people on and off the court</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-partners-with-chase-to-award-over--250-000-to-he.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-pledges-800-000-service-hours-in-support-of-mart.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-pledges-800-000-service-hours-in-support-of-mart</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:15:01.248Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation pledges 800,000 service hours in support of Martin Luther King Jr.-inspired “Realize the Dream” movement</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-pledges-800-000-service-hours-in-support-of-mart.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-rally-to-rebuild-campaign.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-rally-to-rebuild-campaign</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:15:08.775Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation launches 'Rally to Rebuild' campaign</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-rally-to-rebuild-campaign.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-receives-transformative-2-7-million-gift-from-t.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-receives-transformative-2-7-million-gift-from-t</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:15:17.218Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation receives transformative $2.7 million gift from the Chess Foundation</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-receives-transformative--2-7-million-gift-from-t.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-reginald-f-lewis-foundation-announce-inaugural.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-reginald-f-lewis-foundation-announce-inaugural</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:13:43.246Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation, Reginald F. Lewis Foundation announce inaugural recipients of Reginald F. Lewis Game Changer Award</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation--reginald-f--lewis-foundation-announce-inaugural.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-scholarship-recipients-meet-billie-jean-king-at-0.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-scholarship-recipients-meet-billie-jean-king-at-0</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:15:29.810Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation scholarship recipients meet Billie Jean King at the 2026 US Open</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-scholarship-recipients-meet-billie-jean-king-at-0.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-scholarship-recipients-meet-billie-jean-king-at.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-scholarship-recipients-meet-billie-jean-king-at</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:15:23.636Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation scholarship recipients meet Billie Jean King at the 2025 US Open</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-scholarship-recipients-meet-billie-jean-king-at-.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-teams-up-with-la-roche-posay-for-events-at-selec.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-teams-up-with-la-roche-posay-for-events-at-selec</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:15:35.980Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation teams up with La Roche-Posay for events at select NJTL chapters</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-teams-up-with-la-roche-posay-for-events-at-selec.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-to-celebrate-winners-of-2025-national-junior-ten.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-to-celebrate-winners-of-2025-national-junior-ten</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:15:43.658Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation to celebrate winners of 2025 NJTL Essay Contest during US Open Fan Week</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-to-celebrate-winners-of-2025-national-junior-ten.html</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-to-honor-andre-agassi-with-serving-up-dreams-awa.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/usta-foundation-to-honor-andre-agassi-with-serving-up-dreams-awa</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:15:50.241Z</t>
+  </si>
+  <si>
+    <t>USTA Foundation to honor Andre Agassi with Serving Up Dreams Award at the 2025 US Open</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/usta-foundation-to-honor-andre-agassi-with-serving-up-dreams-awa.html</t>
+  </si>
+  <si>
+    <t>en/home/news/what-s-the-why-former-atp-wta-pros-open-up-on-their-support-of.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/what-s-the-why-former-atp-wta-pros-open-up-on-their-support-of</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:15:56.594Z</t>
+  </si>
+  <si>
+    <t>What’s the why? Former ATP, WTA pros open up on their support of the USTA Foundation</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/what-s-the-why--former-atp--wta-pros-open-up-on-their-support-of.html</t>
+  </si>
+  <si>
+    <t>en/home/news/women-s-history-month-2026-how-two-community-impact-hub-leaders.report.json</t>
+  </si>
+  <si>
+    <t>en/home/news/women-s-history-month-2026-how-two-community-impact-hub-leaders</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:16:04.156Z</t>
+  </si>
+  <si>
+    <t>Women’s History Month 2026: How two Community Impact Hub leaders are using the power of tennis to inspire youth in Atlanta</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news/women-s-history-month-2026--how-two-community-impact-hub-leaders.html</t>
   </si>
 </sst>
 </file>
@@ -468,16 +1595,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="50" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="8" width="50" customWidth="1"/>
+    <col min="1" max="5" width="50" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="10" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -502,61 +1629,2383 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" t="s">
+        <v>91</v>
+      </c>
+      <c r="J15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" t="s">
+        <v>107</v>
+      </c>
+      <c r="J18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" t="s">
+        <v>111</v>
+      </c>
+      <c r="I19" t="s">
+        <v>112</v>
+      </c>
+      <c r="J19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" t="s">
+        <v>116</v>
+      </c>
+      <c r="I20" t="s">
+        <v>117</v>
+      </c>
+      <c r="J20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" t="s">
+        <v>121</v>
+      </c>
+      <c r="I21" t="s">
+        <v>122</v>
+      </c>
+      <c r="J21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" t="s">
+        <v>127</v>
+      </c>
+      <c r="J22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>130</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23" t="s">
+        <v>132</v>
+      </c>
+      <c r="J23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" t="s">
+        <v>137</v>
+      </c>
+      <c r="J24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>139</v>
+      </c>
+      <c r="B25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" t="s">
+        <v>141</v>
+      </c>
+      <c r="I25" t="s">
+        <v>142</v>
+      </c>
+      <c r="J25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>145</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" t="s">
+        <v>146</v>
+      </c>
+      <c r="I26" t="s">
+        <v>147</v>
+      </c>
+      <c r="J26" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" t="s">
+        <v>151</v>
+      </c>
+      <c r="I27" t="s">
+        <v>152</v>
+      </c>
+      <c r="J27" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" t="s">
+        <v>156</v>
+      </c>
+      <c r="I28" t="s">
+        <v>157</v>
+      </c>
+      <c r="J28" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" t="s">
+        <v>161</v>
+      </c>
+      <c r="I29" t="s">
+        <v>162</v>
+      </c>
+      <c r="J29" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>164</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>165</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" t="s">
+        <v>166</v>
+      </c>
+      <c r="I30" t="s">
+        <v>167</v>
+      </c>
+      <c r="J30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>169</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>170</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" t="s">
+        <v>171</v>
+      </c>
+      <c r="I31" t="s">
+        <v>172</v>
+      </c>
+      <c r="J31" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>174</v>
+      </c>
+      <c r="B32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>175</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" t="s">
+        <v>176</v>
+      </c>
+      <c r="I32" t="s">
+        <v>177</v>
+      </c>
+      <c r="J32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" t="s">
+        <v>180</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>181</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" t="s">
+        <v>182</v>
+      </c>
+      <c r="I33" t="s">
+        <v>183</v>
+      </c>
+      <c r="J33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>186</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" t="s">
+        <v>187</v>
+      </c>
+      <c r="I34" t="s">
+        <v>188</v>
+      </c>
+      <c r="J34" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>191</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" t="s">
+        <v>192</v>
+      </c>
+      <c r="I35" t="s">
+        <v>193</v>
+      </c>
+      <c r="J35" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s">
+        <v>196</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" t="s">
+        <v>197</v>
+      </c>
+      <c r="I36" t="s">
+        <v>198</v>
+      </c>
+      <c r="J36" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>200</v>
+      </c>
+      <c r="B37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
+        <v>201</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" t="s">
+        <v>202</v>
+      </c>
+      <c r="I37" t="s">
+        <v>203</v>
+      </c>
+      <c r="J37" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>205</v>
+      </c>
+      <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" t="s">
+        <v>206</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" t="s">
+        <v>207</v>
+      </c>
+      <c r="I38" t="s">
+        <v>208</v>
+      </c>
+      <c r="J38" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>210</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>211</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" t="s">
+        <v>212</v>
+      </c>
+      <c r="I39" t="s">
+        <v>213</v>
+      </c>
+      <c r="J39" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>216</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" t="s">
+        <v>217</v>
+      </c>
+      <c r="I40" t="s">
+        <v>218</v>
+      </c>
+      <c r="J40" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>220</v>
+      </c>
+      <c r="B41" t="s">
+        <v>221</v>
+      </c>
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>222</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>22</v>
+      </c>
+      <c r="H41" t="s">
+        <v>223</v>
+      </c>
+      <c r="I41" t="s">
+        <v>224</v>
+      </c>
+      <c r="J41" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>226</v>
+      </c>
+      <c r="B42" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
+        <v>227</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" t="s">
+        <v>228</v>
+      </c>
+      <c r="I42" t="s">
+        <v>103</v>
+      </c>
+      <c r="J42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>230</v>
+      </c>
+      <c r="B43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>231</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s">
+        <v>22</v>
+      </c>
+      <c r="H43" t="s">
+        <v>232</v>
+      </c>
+      <c r="I43" t="s">
+        <v>233</v>
+      </c>
+      <c r="J43" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>235</v>
+      </c>
+      <c r="B44" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" t="s">
+        <v>236</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" t="s">
+        <v>22</v>
+      </c>
+      <c r="H44" t="s">
+        <v>237</v>
+      </c>
+      <c r="I44" t="s">
+        <v>238</v>
+      </c>
+      <c r="J44" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>240</v>
+      </c>
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>241</v>
+      </c>
+      <c r="F45" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" t="s">
+        <v>242</v>
+      </c>
+      <c r="I45" t="s">
+        <v>243</v>
+      </c>
+      <c r="J45" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>245</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>246</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" t="s">
+        <v>247</v>
+      </c>
+      <c r="I46" t="s">
+        <v>248</v>
+      </c>
+      <c r="J46" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>250</v>
+      </c>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>251</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47" t="s">
+        <v>252</v>
+      </c>
+      <c r="I47" t="s">
+        <v>253</v>
+      </c>
+      <c r="J47" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>255</v>
+      </c>
+      <c r="B48" t="s">
+        <v>256</v>
+      </c>
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
+        <v>257</v>
+      </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" t="s">
+        <v>258</v>
+      </c>
+      <c r="I48" t="s">
+        <v>259</v>
+      </c>
+      <c r="J48" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>261</v>
+      </c>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" t="s">
+        <v>262</v>
+      </c>
+      <c r="F49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49" t="s">
+        <v>263</v>
+      </c>
+      <c r="I49" t="s">
+        <v>264</v>
+      </c>
+      <c r="J49" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>266</v>
+      </c>
+      <c r="B50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>267</v>
+      </c>
+      <c r="F50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" t="s">
+        <v>268</v>
+      </c>
+      <c r="I50" t="s">
+        <v>269</v>
+      </c>
+      <c r="J50" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>271</v>
+      </c>
+      <c r="B51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>272</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>22</v>
+      </c>
+      <c r="H51" t="s">
+        <v>273</v>
+      </c>
+      <c r="I51" t="s">
+        <v>274</v>
+      </c>
+      <c r="J51" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>276</v>
+      </c>
+      <c r="B52" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" t="s">
+        <v>277</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" t="s">
+        <v>22</v>
+      </c>
+      <c r="H52" t="s">
+        <v>278</v>
+      </c>
+      <c r="I52" t="s">
+        <v>279</v>
+      </c>
+      <c r="J52" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>281</v>
+      </c>
+      <c r="B53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" t="s">
+        <v>282</v>
+      </c>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" t="s">
+        <v>283</v>
+      </c>
+      <c r="I53" t="s">
+        <v>284</v>
+      </c>
+      <c r="J53" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>286</v>
+      </c>
+      <c r="B54" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
+        <v>287</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" t="s">
+        <v>288</v>
+      </c>
+      <c r="I54" t="s">
+        <v>289</v>
+      </c>
+      <c r="J54" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>291</v>
+      </c>
+      <c r="B55" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" t="s">
+        <v>292</v>
+      </c>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" t="s">
+        <v>293</v>
+      </c>
+      <c r="I55" t="s">
+        <v>294</v>
+      </c>
+      <c r="J55" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>296</v>
+      </c>
+      <c r="B56" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" t="s">
+        <v>297</v>
+      </c>
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" t="s">
+        <v>298</v>
+      </c>
+      <c r="I56" t="s">
+        <v>299</v>
+      </c>
+      <c r="J56" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>301</v>
+      </c>
+      <c r="B57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" t="s">
+        <v>302</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" t="s">
+        <v>303</v>
+      </c>
+      <c r="I57" t="s">
+        <v>304</v>
+      </c>
+      <c r="J57" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>306</v>
+      </c>
+      <c r="B58" t="s">
+        <v>51</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>307</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" t="s">
+        <v>308</v>
+      </c>
+      <c r="I58" t="s">
+        <v>309</v>
+      </c>
+      <c r="J58" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>311</v>
+      </c>
+      <c r="B59" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" t="s">
+        <v>312</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" t="s">
+        <v>313</v>
+      </c>
+      <c r="I59" t="s">
+        <v>314</v>
+      </c>
+      <c r="J59" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>316</v>
+      </c>
+      <c r="B60" t="s">
+        <v>57</v>
+      </c>
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>317</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s">
+        <v>22</v>
+      </c>
+      <c r="H60" t="s">
+        <v>318</v>
+      </c>
+      <c r="I60" t="s">
+        <v>319</v>
+      </c>
+      <c r="J60" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>321</v>
+      </c>
+      <c r="B61" t="s">
+        <v>322</v>
+      </c>
+      <c r="C61" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>323</v>
+      </c>
+      <c r="F61" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" t="s">
+        <v>324</v>
+      </c>
+      <c r="I61" t="s">
+        <v>325</v>
+      </c>
+      <c r="J61" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>327</v>
+      </c>
+      <c r="B62" t="s">
+        <v>180</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" t="s">
+        <v>328</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" t="s">
+        <v>329</v>
+      </c>
+      <c r="I62" t="s">
+        <v>330</v>
+      </c>
+      <c r="J62" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>332</v>
+      </c>
+      <c r="B63" t="s">
+        <v>333</v>
+      </c>
+      <c r="C63" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s">
+        <v>334</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" t="s">
+        <v>335</v>
+      </c>
+      <c r="I63" t="s">
+        <v>336</v>
+      </c>
+      <c r="J63" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>338</v>
+      </c>
+      <c r="B64" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" t="s">
+        <v>339</v>
+      </c>
+      <c r="F64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" t="s">
+        <v>340</v>
+      </c>
+      <c r="I64" t="s">
+        <v>341</v>
+      </c>
+      <c r="J64" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>343</v>
+      </c>
+      <c r="B65" t="s">
+        <v>256</v>
+      </c>
+      <c r="C65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" t="s">
+        <v>344</v>
+      </c>
+      <c r="F65" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65" t="s">
+        <v>22</v>
+      </c>
+      <c r="H65" t="s">
+        <v>345</v>
+      </c>
+      <c r="I65" t="s">
+        <v>346</v>
+      </c>
+      <c r="J65" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>348</v>
+      </c>
+      <c r="B66" t="s">
+        <v>57</v>
+      </c>
+      <c r="C66" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" t="s">
+        <v>349</v>
+      </c>
+      <c r="F66" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" t="s">
+        <v>22</v>
+      </c>
+      <c r="H66" t="s">
+        <v>350</v>
+      </c>
+      <c r="I66" t="s">
+        <v>351</v>
+      </c>
+      <c r="J66" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>353</v>
+      </c>
+      <c r="B67" t="s">
+        <v>57</v>
+      </c>
+      <c r="C67" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" t="s">
+        <v>354</v>
+      </c>
+      <c r="F67" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" t="s">
+        <v>355</v>
+      </c>
+      <c r="I67" t="s">
+        <v>356</v>
+      </c>
+      <c r="J67" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>358</v>
+      </c>
+      <c r="B68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" t="s">
+        <v>359</v>
+      </c>
+      <c r="F68" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" t="s">
+        <v>22</v>
+      </c>
+      <c r="H68" t="s">
+        <v>360</v>
+      </c>
+      <c r="I68" t="s">
+        <v>361</v>
+      </c>
+      <c r="J68" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>363</v>
+      </c>
+      <c r="B69" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" t="s">
+        <v>364</v>
+      </c>
+      <c r="F69" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" t="s">
+        <v>22</v>
+      </c>
+      <c r="H69" t="s">
+        <v>365</v>
+      </c>
+      <c r="I69" t="s">
+        <v>366</v>
+      </c>
+      <c r="J69" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>368</v>
+      </c>
+      <c r="B70" t="s">
+        <v>180</v>
+      </c>
+      <c r="C70" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" t="s">
+        <v>369</v>
+      </c>
+      <c r="F70" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" t="s">
+        <v>22</v>
+      </c>
+      <c r="H70" t="s">
+        <v>370</v>
+      </c>
+      <c r="I70" t="s">
+        <v>371</v>
+      </c>
+      <c r="J70" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>373</v>
+      </c>
+      <c r="B71" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" t="s">
+        <v>374</v>
+      </c>
+      <c r="F71" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" t="s">
+        <v>22</v>
+      </c>
+      <c r="H71" t="s">
+        <v>375</v>
+      </c>
+      <c r="I71" t="s">
+        <v>376</v>
+      </c>
+      <c r="J71" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>378</v>
+      </c>
+      <c r="B72" t="s">
+        <v>180</v>
+      </c>
+      <c r="C72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" t="s">
+        <v>379</v>
+      </c>
+      <c r="F72" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" t="s">
+        <v>380</v>
+      </c>
+      <c r="I72" t="s">
+        <v>381</v>
+      </c>
+      <c r="J72" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>383</v>
+      </c>
+      <c r="B73" t="s">
+        <v>180</v>
+      </c>
+      <c r="C73" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" t="s">
+        <v>12</v>
+      </c>
+      <c r="E73" t="s">
+        <v>384</v>
+      </c>
+      <c r="F73" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" t="s">
+        <v>385</v>
+      </c>
+      <c r="I73" t="s">
+        <v>386</v>
+      </c>
+      <c r="J73" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>388</v>
+      </c>
+      <c r="B74" t="s">
+        <v>78</v>
+      </c>
+      <c r="C74" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74" t="s">
+        <v>389</v>
+      </c>
+      <c r="F74" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74" t="s">
+        <v>390</v>
+      </c>
+      <c r="I74" t="s">
+        <v>391</v>
+      </c>
+      <c r="J74" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>393</v>
+      </c>
+      <c r="B75" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" t="s">
+        <v>394</v>
+      </c>
+      <c r="F75" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" t="s">
+        <v>22</v>
+      </c>
+      <c r="H75" t="s">
+        <v>395</v>
+      </c>
+      <c r="I75" t="s">
+        <v>396</v>
+      </c>
+      <c r="J75" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-news-v1.report.xlsx
+++ b/tools/importer/reports/import-news-v1.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="399">
   <si>
     <t>_reportFile</t>
   </si>
@@ -82,7 +82,7 @@
     <t>news</t>
   </si>
   <si>
-    <t>2026-09-07T16:26:50.132Z</t>
+    <t>2026-09-08T04:53:14.859Z</t>
   </si>
   <si>
     <t>2023 NJTL Essay Contest Winners</t>
@@ -378,7 +378,7 @@
     <t>en/home/news/frances-tiafoe-fund-surpasses-1-million-raised</t>
   </si>
   <si>
-    <t>2026-09-07T17:10:43.425Z</t>
+    <t>2026-09-08T04:33:38.451Z</t>
   </si>
   <si>
     <t>Frances Tiafoe Fund surpasses $1 million raised</t>
@@ -420,10 +420,13 @@
     <t>en/home/news/how-the-usta-foundation-and-realize-the-dream-are-set-to-inspire.report.json</t>
   </si>
   <si>
+    <t>["cards-news","social","reactions","instagram-split×1","columns-media×1"]</t>
+  </si>
+  <si>
     <t>en/home/news/how-the-usta-foundation-and-realize-the-dream-are-set-to-inspire</t>
   </si>
   <si>
-    <t>2026-09-07T17:11:02.584Z</t>
+    <t>2026-09-08T04:40:43.478Z</t>
   </si>
   <si>
     <t>How the USTA Foundation and Realize the Dream are set to inspire a new generation in service and leadership</t>
@@ -543,7 +546,7 @@
     <t>en/home/news/laver-cup-community-legacy-project-celebrates-court-unveiling-at</t>
   </si>
   <si>
-    <t>2026-09-07T14:26:59.025Z</t>
+    <t>2026-09-08T04:35:16.114Z</t>
   </si>
   <si>
     <t>Laver Cup Community Legacy Project celebrates court unveiling at John McLaren Park</t>
@@ -636,7 +639,7 @@
     <t>en/home/news/newport-njtl-honor-chris-evert</t>
   </si>
   <si>
-    <t>2026-09-07T17:12:30.053Z</t>
+    <t>2026-09-08T04:46:47.185Z</t>
   </si>
   <si>
     <t>Home of Newport NJTL named in honor of Chris Evert</t>
@@ -651,7 +654,7 @@
     <t>en/home/news/ngounoue-excellence-team-junior-french-open</t>
   </si>
   <si>
-    <t>2026-09-07T19:03:11.452Z</t>
+    <t>2026-09-08T04:47:57.400Z</t>
   </si>
   <si>
     <t>Montgomery, Ngounoue represent Excellence Team at junior French Open</t>
@@ -666,7 +669,7 @@
     <t>en/home/news/njtl-ace-jabeiro-brown</t>
   </si>
   <si>
-    <t>2026-09-07T16:09:08.458Z</t>
+    <t>2026-09-08T04:35:10.310Z</t>
   </si>
   <si>
     <t>From New York to UCF: Catching up with NJTL ace Jabeiro Brown</t>
@@ -921,10 +924,13 @@
     <t>en/home/news/usta-foundation-celebrates-2026-njtl-essay-contest-winners-at-us.report.json</t>
   </si>
   <si>
+    <t>["cards-news","social","table-grade×1","columns-media×1"]</t>
+  </si>
+  <si>
     <t>en/home/news/usta-foundation-celebrates-2026-njtl-essay-contest-winners-at-us</t>
   </si>
   <si>
-    <t>2026-09-07T17:14:20.641Z</t>
+    <t>2026-09-08T05:09:55.395Z</t>
   </si>
   <si>
     <t>USTA Foundation celebrates 2026 NJTL essay contest winners at US Open Fan Week experience presented by Deloitte</t>
@@ -981,13 +987,13 @@
     <t>en/home/news/usta-foundation-launches-community-impact-hub-initiative.report.json</t>
   </si>
   <si>
-    <t>["cards-news","reactions","video-embed×1"]</t>
+    <t>["cards-news","reactions","video-embed×1","columns-media×1"]</t>
   </si>
   <si>
     <t>en/home/news/usta-foundation-launches-community-impact-hub-initiative</t>
   </si>
   <si>
-    <t>2026-09-07T14:01:09.347Z</t>
+    <t>2026-09-08T04:57:23.231Z</t>
   </si>
   <si>
     <t>USTA Foundation launches Community Impact Hub initiative</t>
@@ -1014,13 +1020,10 @@
     <t>en/home/news/usta-foundation-offline-by-aerie-and-the-aerie-real-foundatio.report.json</t>
   </si>
   <si>
-    <t>["social","cards-news"]</t>
-  </si>
-  <si>
     <t>en/home/news/usta-foundation-offline-by-aerie-and-the-aerie-real-foundatio</t>
   </si>
   <si>
-    <t>2026-09-07T10:27:10.543Z</t>
+    <t>2026-09-08T04:35:23.260Z</t>
   </si>
   <si>
     <t>USTA Foundation, OFFLINE by Aerie® and the Aerie Real Foundation™ partner to empower next generation of women in tennis</t>
@@ -1050,7 +1053,7 @@
     <t>en/home/news/usta-foundation-pledges-800-000-service-hours-in-support-of-mart</t>
   </si>
   <si>
-    <t>2026-09-07T17:15:01.248Z</t>
+    <t>2026-09-08T04:56:31.065Z</t>
   </si>
   <si>
     <t>USTA Foundation pledges 800,000 service hours in support of Martin Luther King Jr.-inspired “Realize the Dream” movement</t>
@@ -2345,7 +2348,7 @@
         <v>134</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -2354,7 +2357,7 @@
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F24" t="s">
         <v>14</v>
@@ -2363,18 +2366,18 @@
         <v>22</v>
       </c>
       <c r="H24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B25" t="s">
         <v>57</v>
@@ -2386,7 +2389,7 @@
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
@@ -2395,18 +2398,18 @@
         <v>22</v>
       </c>
       <c r="H25" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B26" t="s">
         <v>57</v>
@@ -2418,7 +2421,7 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
@@ -2427,18 +2430,18 @@
         <v>22</v>
       </c>
       <c r="H26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
@@ -2450,7 +2453,7 @@
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
@@ -2459,18 +2462,18 @@
         <v>22</v>
       </c>
       <c r="H27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
@@ -2482,7 +2485,7 @@
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
@@ -2491,18 +2494,18 @@
         <v>22</v>
       </c>
       <c r="H28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s">
         <v>57</v>
@@ -2514,7 +2517,7 @@
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
@@ -2523,18 +2526,18 @@
         <v>22</v>
       </c>
       <c r="H29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I29" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s">
         <v>57</v>
@@ -2546,7 +2549,7 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
@@ -2555,18 +2558,18 @@
         <v>22</v>
       </c>
       <c r="H30" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J30" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s">
         <v>33</v>
@@ -2578,7 +2581,7 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
@@ -2587,18 +2590,18 @@
         <v>22</v>
       </c>
       <c r="H31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J31" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s">
         <v>57</v>
@@ -2610,7 +2613,7 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
@@ -2619,21 +2622,21 @@
         <v>22</v>
       </c>
       <c r="H32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -2642,7 +2645,7 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
@@ -2651,18 +2654,18 @@
         <v>22</v>
       </c>
       <c r="H33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B34" t="s">
         <v>33</v>
@@ -2674,7 +2677,7 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
@@ -2683,18 +2686,18 @@
         <v>22</v>
       </c>
       <c r="H34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I34" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J34" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s">
         <v>33</v>
@@ -2706,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
@@ -2715,18 +2718,18 @@
         <v>22</v>
       </c>
       <c r="H35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J35" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B36" t="s">
         <v>57</v>
@@ -2738,7 +2741,7 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F36" t="s">
         <v>14</v>
@@ -2747,18 +2750,18 @@
         <v>22</v>
       </c>
       <c r="H36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B37" t="s">
         <v>33</v>
@@ -2770,7 +2773,7 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
@@ -2779,21 +2782,21 @@
         <v>22</v>
       </c>
       <c r="H37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J37" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -2802,7 +2805,7 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
@@ -2811,18 +2814,18 @@
         <v>22</v>
       </c>
       <c r="H38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J38" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s">
         <v>51</v>
@@ -2834,7 +2837,7 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
@@ -2843,18 +2846,18 @@
         <v>22</v>
       </c>
       <c r="H39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B40" t="s">
         <v>78</v>
@@ -2866,7 +2869,7 @@
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
@@ -2875,21 +2878,21 @@
         <v>22</v>
       </c>
       <c r="H40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B41" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
@@ -2898,7 +2901,7 @@
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
@@ -2907,18 +2910,18 @@
         <v>22</v>
       </c>
       <c r="H41" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I41" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J41" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B42" t="s">
         <v>57</v>
@@ -2930,7 +2933,7 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
@@ -2939,18 +2942,18 @@
         <v>22</v>
       </c>
       <c r="H42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I42" t="s">
         <v>103</v>
       </c>
       <c r="J42" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B43" t="s">
         <v>57</v>
@@ -2962,7 +2965,7 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
@@ -2971,18 +2974,18 @@
         <v>22</v>
       </c>
       <c r="H43" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I43" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J43" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B44" t="s">
         <v>57</v>
@@ -2994,7 +2997,7 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
@@ -3003,18 +3006,18 @@
         <v>22</v>
       </c>
       <c r="H44" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I44" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J44" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B45" t="s">
         <v>57</v>
@@ -3026,7 +3029,7 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
@@ -3035,18 +3038,18 @@
         <v>22</v>
       </c>
       <c r="H45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J45" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B46" t="s">
         <v>57</v>
@@ -3058,7 +3061,7 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
@@ -3067,18 +3070,18 @@
         <v>22</v>
       </c>
       <c r="H46" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I46" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J46" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B47" t="s">
         <v>57</v>
@@ -3090,7 +3093,7 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
@@ -3099,21 +3102,21 @@
         <v>22</v>
       </c>
       <c r="H47" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I47" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J47" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B48" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
@@ -3122,7 +3125,7 @@
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
@@ -3131,18 +3134,18 @@
         <v>22</v>
       </c>
       <c r="H48" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I48" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B49" t="s">
         <v>57</v>
@@ -3154,7 +3157,7 @@
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F49" t="s">
         <v>14</v>
@@ -3163,18 +3166,18 @@
         <v>22</v>
       </c>
       <c r="H49" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I49" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J49" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B50" t="s">
         <v>27</v>
@@ -3186,7 +3189,7 @@
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
@@ -3195,18 +3198,18 @@
         <v>22</v>
       </c>
       <c r="H50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B51" t="s">
         <v>57</v>
@@ -3218,7 +3221,7 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
@@ -3227,18 +3230,18 @@
         <v>22</v>
       </c>
       <c r="H51" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I51" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J51" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B52" t="s">
         <v>57</v>
@@ -3250,7 +3253,7 @@
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F52" t="s">
         <v>14</v>
@@ -3259,18 +3262,18 @@
         <v>22</v>
       </c>
       <c r="H52" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I52" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B53" t="s">
         <v>27</v>
@@ -3282,7 +3285,7 @@
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F53" t="s">
         <v>14</v>
@@ -3291,18 +3294,18 @@
         <v>22</v>
       </c>
       <c r="H53" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I53" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J53" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B54" t="s">
         <v>57</v>
@@ -3314,7 +3317,7 @@
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F54" t="s">
         <v>14</v>
@@ -3323,18 +3326,18 @@
         <v>22</v>
       </c>
       <c r="H54" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I54" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J54" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B55" t="s">
         <v>57</v>
@@ -3346,7 +3349,7 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
@@ -3355,18 +3358,18 @@
         <v>22</v>
       </c>
       <c r="H55" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I55" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J55" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B56" t="s">
         <v>27</v>
@@ -3378,7 +3381,7 @@
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F56" t="s">
         <v>14</v>
@@ -3387,21 +3390,21 @@
         <v>22</v>
       </c>
       <c r="H56" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I56" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J56" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B57" t="s">
-        <v>27</v>
+        <v>303</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
@@ -3410,7 +3413,7 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F57" t="s">
         <v>14</v>
@@ -3419,18 +3422,18 @@
         <v>22</v>
       </c>
       <c r="H57" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I57" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J57" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B58" t="s">
         <v>51</v>
@@ -3442,7 +3445,7 @@
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
@@ -3451,18 +3454,18 @@
         <v>22</v>
       </c>
       <c r="H58" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I58" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J58" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B59" t="s">
         <v>51</v>
@@ -3474,7 +3477,7 @@
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F59" t="s">
         <v>14</v>
@@ -3483,18 +3486,18 @@
         <v>22</v>
       </c>
       <c r="H59" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I59" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B60" t="s">
         <v>57</v>
@@ -3506,7 +3509,7 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
@@ -3515,21 +3518,21 @@
         <v>22</v>
       </c>
       <c r="H60" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I60" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J60" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B61" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C61" t="s">
         <v>12</v>
@@ -3538,7 +3541,7 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F61" t="s">
         <v>14</v>
@@ -3547,21 +3550,21 @@
         <v>22</v>
       </c>
       <c r="H61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I61" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J61" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B62" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C62" t="s">
         <v>12</v>
@@ -3570,7 +3573,7 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F62" t="s">
         <v>14</v>
@@ -3579,21 +3582,21 @@
         <v>22</v>
       </c>
       <c r="H62" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I62" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J62" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B63" t="s">
-        <v>333</v>
+        <v>27</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
@@ -3602,7 +3605,7 @@
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F63" t="s">
         <v>14</v>
@@ -3611,18 +3614,18 @@
         <v>22</v>
       </c>
       <c r="H63" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I63" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J63" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B64" t="s">
         <v>27</v>
@@ -3634,7 +3637,7 @@
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F64" t="s">
         <v>14</v>
@@ -3643,21 +3646,21 @@
         <v>22</v>
       </c>
       <c r="H64" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I64" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J64" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B65" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C65" t="s">
         <v>12</v>
@@ -3666,7 +3669,7 @@
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F65" t="s">
         <v>14</v>
@@ -3675,18 +3678,18 @@
         <v>22</v>
       </c>
       <c r="H65" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I65" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J65" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B66" t="s">
         <v>57</v>
@@ -3698,7 +3701,7 @@
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F66" t="s">
         <v>14</v>
@@ -3707,18 +3710,18 @@
         <v>22</v>
       </c>
       <c r="H66" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J66" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B67" t="s">
         <v>57</v>
@@ -3730,7 +3733,7 @@
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F67" t="s">
         <v>14</v>
@@ -3739,18 +3742,18 @@
         <v>22</v>
       </c>
       <c r="H67" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I67" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J67" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B68" t="s">
         <v>27</v>
@@ -3762,7 +3765,7 @@
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F68" t="s">
         <v>14</v>
@@ -3771,18 +3774,18 @@
         <v>22</v>
       </c>
       <c r="H68" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I68" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J68" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B69" t="s">
         <v>27</v>
@@ -3794,7 +3797,7 @@
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F69" t="s">
         <v>14</v>
@@ -3803,21 +3806,21 @@
         <v>22</v>
       </c>
       <c r="H69" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I69" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J69" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B70" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
@@ -3826,7 +3829,7 @@
         <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F70" t="s">
         <v>14</v>
@@ -3835,18 +3838,18 @@
         <v>22</v>
       </c>
       <c r="H70" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I70" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J70" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B71" t="s">
         <v>57</v>
@@ -3858,7 +3861,7 @@
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F71" t="s">
         <v>14</v>
@@ -3867,21 +3870,21 @@
         <v>22</v>
       </c>
       <c r="H71" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I71" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J71" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B72" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C72" t="s">
         <v>12</v>
@@ -3890,7 +3893,7 @@
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F72" t="s">
         <v>14</v>
@@ -3899,21 +3902,21 @@
         <v>22</v>
       </c>
       <c r="H72" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I72" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J72" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B73" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C73" t="s">
         <v>12</v>
@@ -3922,7 +3925,7 @@
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F73" t="s">
         <v>14</v>
@@ -3931,18 +3934,18 @@
         <v>22</v>
       </c>
       <c r="H73" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I73" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J73" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B74" t="s">
         <v>78</v>
@@ -3954,7 +3957,7 @@
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F74" t="s">
         <v>14</v>
@@ -3963,18 +3966,18 @@
         <v>22</v>
       </c>
       <c r="H74" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I74" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J74" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B75" t="s">
         <v>33</v>
@@ -3986,7 +3989,7 @@
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F75" t="s">
         <v>14</v>
@@ -3995,13 +3998,13 @@
         <v>22</v>
       </c>
       <c r="H75" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I75" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J75" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-news-v1.report.xlsx
+++ b/tools/importer/reports/import-news-v1.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="475">
   <si>
     <t>_reportFile</t>
   </si>
@@ -68,6 +68,164 @@
   </si>
   <si>
     <t>https://www.ustafoundation.com/en/home.html</t>
+  </si>
+  <si>
+    <t>en/home/get-involved.report.json</t>
+  </si>
+  <si>
+    <t>["hero-text-up","default-content(gift-intro)","columns(individual,image-right)","spacer(yellow-strip)","columns(impact,image-left,yellow)","columns(ypi,image-right)","spacer(yellow-strip)","columns(planned,image-left,yellow)","cards-content(signature-events)","spacer(yellow-strip)","columns(corporate,image-left,yellow,center-intro)","spacer(trailing-black-band)"]</t>
+  </si>
+  <si>
+    <t>en/home/get-involved</t>
+  </si>
+  <si>
+    <t>general</t>
+  </si>
+  <si>
+    <t>2026-09-08T18:52:19.627Z</t>
+  </si>
+  <si>
+    <t>Get Involved</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/get-involved.html</t>
+  </si>
+  <si>
+    <t>en/home/news.report.json</t>
+  </si>
+  <si>
+    <t>["(blank — matches empty source)"]</t>
+  </si>
+  <si>
+    <t>en/home/news</t>
+  </si>
+  <si>
+    <t>2026-09-08T20:57:14.669Z</t>
+  </si>
+  <si>
+    <t>News</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/news.html</t>
+  </si>
+  <si>
+    <t>en/home/our-impact.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","default-content(not-ready-intro)","columns(not-ready-stats,image-right)","spacer(yellow-strip)","columns(reach,image-left,yellow,center-intro)","banner-stats-grid","spacer(yellow-strip)","cards-stats(yellow,center)","spacer(trailing-black-band)"]</t>
+  </si>
+  <si>
+    <t>en/home/our-impact</t>
+  </si>
+  <si>
+    <t>2026-09-08T18:52:55.531Z</t>
+  </si>
+  <si>
+    <t>Our Impact</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/our-impact.html</t>
+  </si>
+  <si>
+    <t>en/home/what-we-do.html.report.json</t>
+  </si>
+  <si>
+    <t>page.goto: Target page, context or browser has been closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.goto: Target page, context or browser has been closed
+    at processUrl (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:597:20)
+    at async main (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:954:22)</t>
+  </si>
+  <si>
+    <t>en/home/what-we-do.html</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-09-08T18:53:07.322Z</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/what-we-do.html</t>
+  </si>
+  <si>
+    <t>en/home/what-we-do.report.json</t>
+  </si>
+  <si>
+    <t>["hero-text-up","default-content(priorities-intro)","cards-content(priorities)","spacer(yellow-strip)","columns(transform,image-left,yellow,center-intro)","default-content(njtl-map)","default-content(sustained-intro)","cards-content(sustained)","spacer(trailing-black-band)"]</t>
+  </si>
+  <si>
+    <t>en/home/what-we-do</t>
+  </si>
+  <si>
+    <t>2026-09-08T18:54:14.235Z</t>
+  </si>
+  <si>
+    <t>What We Do</t>
+  </si>
+  <si>
+    <t>en/home/who-we-are.html.report.json</t>
+  </si>
+  <si>
+    <t>en/home/who-we-are.html</t>
+  </si>
+  <si>
+    <t>2026-09-08T10:56:37.022Z</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/who-we-are.html</t>
+  </si>
+  <si>
+    <t>en/home/who-we-are.report.json</t>
+  </si>
+  <si>
+    <t>["hero-text-up","default-content(intro)","columns(history,image-right)","spacer(leading-yellow-strip)","columns(evert,image-left)","section-metadata(yellow-band)","default-content(supporters)","cards-tiles","spacer(trailing-black-band)"]</t>
+  </si>
+  <si>
+    <t>en/home/who-we-are</t>
+  </si>
+  <si>
+    <t>2026-09-08T18:51:42.954Z</t>
+  </si>
+  <si>
+    <t>Who We Are</t>
+  </si>
+  <si>
+    <t>en/home/get-involved/special-funds.report.json</t>
+  </si>
+  <si>
+    <t>["hero-text-up","fund(tiafoe,image-right,center-intro)","spacer(yellow-strip)","fund(mackie,image-left,yellow)","fund(evert,image-right,center-intro)","spacer(above-cards-expand)","cards-expand","spacer(trailing-black-band)"]</t>
+  </si>
+  <si>
+    <t>en/home/get-involved/special-funds</t>
+  </si>
+  <si>
+    <t>2026-09-08T18:55:06.933Z</t>
+  </si>
+  <si>
+    <t>Special Funds</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/get-involved/special-funds.html</t>
+  </si>
+  <si>
+    <t>en/home/get-involved/young-professional-initiative.report.json</t>
+  </si>
+  <si>
+    <t>["hero-text-up-tall","center-intro(future-of-giving)","columns(what-is-ypi,image-right)","spacer(yellow-strip)","columns(impact,image-left,yellow)","quote-image(labanowski)","spacer(yellow-strip)","columns(ways,image-left,yellow)","spacer(trailing-black-band)"]</t>
+  </si>
+  <si>
+    <t>en/home/get-involved/young-professional-initiative</t>
+  </si>
+  <si>
+    <t>2026-09-08T22:47:49.236Z</t>
+  </si>
+  <si>
+    <t>Young Professional Initiative</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/get-involved/young-professional-initiative.html</t>
   </si>
   <si>
     <t>en/home/news/2023-njtl-essay-contest-winners.report.json</t>
@@ -306,9 +464,6 @@
     <t>en/home/news/evert-speaks-on-rally-to-rebuild.html</t>
   </si>
   <si>
-    <t>failed</t>
-  </si>
-  <si>
     <t>2026-09-07T17:08:09.871Z</t>
   </si>
   <si>
@@ -774,7 +929,7 @@
     <t>en/home/news/robin-montgomery-wimbledon-debut</t>
   </si>
   <si>
-    <t>2026-09-07T17:13:17.395Z</t>
+    <t>2026-09-09T22:11:28.631Z</t>
   </si>
   <si>
     <t>Excellence Team alumna Robin Montgomery makes Wimbledon debut, earns first Grand Slam main-draw win</t>
@@ -1210,6 +1365,81 @@
   </si>
   <si>
     <t>https://www.ustafoundation.com/en/home/news/women-s-history-month-2026--how-two-community-impact-hub-leaders.html</t>
+  </si>
+  <si>
+    <t>en/home/what-we-do/college-scholarship-opportunities.report.json</t>
+  </si>
+  <si>
+    <t>["hero-text-up","default-content(opening-intro)","cards-content(scholarships)","spacer(yellow-strip)","detail(College Laun,yellow)","detail(College Succ,white)","spacer(yellow-strip)","detail(Novo Nordisk,yellow)","spacer(trailing-black-band)"]</t>
+  </si>
+  <si>
+    <t>en/home/what-we-do/college-scholarship-opportunities</t>
+  </si>
+  <si>
+    <t>2026-09-08T21:20:27.053Z</t>
+  </si>
+  <si>
+    <t>College Scholarship Opportunities</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/what-we-do/college-scholarship-opportunities.html</t>
+  </si>
+  <si>
+    <t>en/home/who-we-are/financials.report.json</t>
+  </si>
+  <si>
+    <t>["default-content(financials)"]</t>
+  </si>
+  <si>
+    <t>en/home/who-we-are/financials</t>
+  </si>
+  <si>
+    <t>2026-09-08T20:04:31.443Z</t>
+  </si>
+  <si>
+    <t>Annual Reports and Financial Information</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/who-we-are/financials.html</t>
+  </si>
+  <si>
+    <t>en/home/who-we-are/leadership-and-staff.report.json</t>
+  </si>
+  <si>
+    <t>["toc-profile","cards-profile(staff)","cards-profile(board)","table-directory","section-metadata(staff)","section-metadata(board)"]</t>
+  </si>
+  <si>
+    <t>en/home/who-we-are/leadership-and-staff</t>
+  </si>
+  <si>
+    <t>leadership</t>
+  </si>
+  <si>
+    <t>2026-09-08T06:19:52.848Z</t>
+  </si>
+  <si>
+    <t>Leadership &amp; Staff</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/who-we-are/leadership-and-staff.html</t>
+  </si>
+  <si>
+    <t>en/home/get-involved/special-funds/chris-evert-50th-anniversary.report.json</t>
+  </si>
+  <si>
+    <t>["default-content(heading,center)","columns(campaign,image-right)","split-even(quote+donate)","spacer(trailing-black-band)"]</t>
+  </si>
+  <si>
+    <t>en/home/get-involved/special-funds/chris-evert-50th-anniversary</t>
+  </si>
+  <si>
+    <t>2026-09-08T21:50:11.450Z</t>
+  </si>
+  <si>
+    <t>Chris Evert 50th anniversary</t>
+  </si>
+  <si>
+    <t>https://www.ustafoundation.com/en/home/get-involved/special-funds/chris-evert-50th-anniversary.html</t>
   </si>
 </sst>
 </file>
@@ -1598,11 +1828,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="10" width="50" customWidth="1"/>
   </cols>
@@ -1772,39 +2002,39 @@
         <v>38</v>
       </c>
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>39</v>
       </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -1813,7 +2043,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
         <v>14</v>
@@ -1822,13 +2052,13 @@
         <v>22</v>
       </c>
       <c r="H7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1836,48 +2066,48 @@
         <v>50</v>
       </c>
       <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
         <v>51</v>
       </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s">
         <v>52</v>
       </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" t="s">
         <v>53</v>
-      </c>
-      <c r="I8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
         <v>56</v>
-      </c>
-      <c r="B9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>58</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
@@ -1886,21 +2116,21 @@
         <v>22</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J9" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -1909,7 +2139,7 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
@@ -1918,30 +2148,30 @@
         <v>22</v>
       </c>
       <c r="H10" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" t="s">
         <v>64</v>
-      </c>
-      <c r="I10" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
         <v>67</v>
-      </c>
-      <c r="B11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>68</v>
       </c>
       <c r="F11" t="s">
         <v>14</v>
@@ -1950,21 +2180,21 @@
         <v>22</v>
       </c>
       <c r="H11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" t="s">
         <v>69</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>70</v>
-      </c>
-      <c r="J11" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
         <v>72</v>
-      </c>
-      <c r="B12" t="s">
-        <v>57</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -1979,24 +2209,24 @@
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -2005,30 +2235,30 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -2037,30 +2267,30 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -2069,62 +2299,62 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H15" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J15" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F16" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="H16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I16" t="s">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="J16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
@@ -2133,30 +2363,30 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H17" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J17" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
@@ -2165,30 +2395,30 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H18" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I18" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J18" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -2197,30 +2427,30 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H19" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="I19" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J19" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -2229,30 +2459,30 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F20" t="s">
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H20" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I20" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J20" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -2261,30 +2491,30 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H21" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I21" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J21" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -2293,30 +2523,30 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H22" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I22" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="J22" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -2325,30 +2555,30 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H23" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="I23" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="J23" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B24" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -2357,62 +2587,62 @@
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F24" t="s">
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H24" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I24" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J24" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="E25" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="G25" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H25" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I25" t="s">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="J25" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -2421,30 +2651,30 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I26" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -2453,30 +2683,30 @@
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H27" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I27" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J27" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
@@ -2485,30 +2715,30 @@
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H28" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="I28" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J28" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
@@ -2517,30 +2747,30 @@
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H29" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="I29" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J29" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -2549,30 +2779,30 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H30" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="I30" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J30" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
@@ -2581,30 +2811,30 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H31" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="I31" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J31" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
@@ -2613,30 +2843,30 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H32" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="I32" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J32" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -2645,30 +2875,30 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H33" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="I33" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J33" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
@@ -2677,30 +2907,30 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H34" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="I34" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J34" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
@@ -2709,30 +2939,30 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H35" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="I35" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="J35" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
         <v>12</v>
@@ -2741,30 +2971,30 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F36" t="s">
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H36" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="I36" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="J36" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
@@ -2773,30 +3003,30 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H37" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="I37" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="J37" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -2805,30 +3035,30 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H38" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="I38" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="J38" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
@@ -2837,30 +3067,30 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H39" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I39" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="J39" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
@@ -2869,30 +3099,30 @@
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H40" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I40" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="J40" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B41" t="s">
-        <v>222</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
@@ -2901,30 +3131,30 @@
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H41" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I41" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J41" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>232</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
@@ -2933,30 +3163,30 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H42" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="I42" t="s">
-        <v>103</v>
+        <v>235</v>
       </c>
       <c r="J42" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -2965,30 +3195,30 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H43" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I43" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J43" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -2997,30 +3227,30 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H44" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="I44" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="J44" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
@@ -3029,30 +3259,30 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H45" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="I45" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="J45" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
@@ -3061,30 +3291,30 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H46" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="I46" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="J46" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>186</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
@@ -3093,30 +3323,30 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H47" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="I47" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="J47" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B48" t="s">
-        <v>257</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
@@ -3125,30 +3355,30 @@
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H48" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I48" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="J48" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="C49" t="s">
         <v>12</v>
@@ -3157,30 +3387,30 @@
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F49" t="s">
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H49" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="I49" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="J49" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>273</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
@@ -3189,30 +3419,30 @@
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H50" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="I50" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="J50" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C51" t="s">
         <v>12</v>
@@ -3221,30 +3451,30 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H51" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="I51" t="s">
-        <v>275</v>
+        <v>154</v>
       </c>
       <c r="J51" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
@@ -3253,30 +3483,30 @@
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F52" t="s">
         <v>14</v>
       </c>
       <c r="G52" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H52" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I52" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="J52" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
@@ -3285,30 +3515,30 @@
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F53" t="s">
         <v>14</v>
       </c>
       <c r="G53" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H53" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I53" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="J53" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B54" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
@@ -3317,30 +3547,30 @@
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F54" t="s">
         <v>14</v>
       </c>
       <c r="G54" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H54" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="I54" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="J54" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
@@ -3349,30 +3579,30 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H55" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="I55" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="J55" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B56" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
@@ -3381,30 +3611,30 @@
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F56" t="s">
         <v>14</v>
       </c>
       <c r="G56" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H56" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I56" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="J56" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B57" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
@@ -3413,30 +3643,30 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F57" t="s">
         <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H57" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="I57" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="J57" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B58" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="C58" t="s">
         <v>12</v>
@@ -3445,30 +3675,30 @@
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H58" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="I58" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J58" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B59" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="C59" t="s">
         <v>12</v>
@@ -3477,30 +3707,30 @@
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F59" t="s">
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H59" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="I59" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="J59" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C60" t="s">
         <v>12</v>
@@ -3509,30 +3739,30 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H60" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="I60" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="J60" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B61" t="s">
-        <v>324</v>
+        <v>109</v>
       </c>
       <c r="C61" t="s">
         <v>12</v>
@@ -3541,30 +3771,30 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F61" t="s">
         <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H61" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I61" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J61" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B62" t="s">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="C62" t="s">
         <v>12</v>
@@ -3573,30 +3803,30 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F62" t="s">
         <v>14</v>
       </c>
       <c r="G62" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H62" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="I62" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J62" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B63" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
@@ -3605,30 +3835,30 @@
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F63" t="s">
         <v>14</v>
       </c>
       <c r="G63" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H63" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="I63" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="J63" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="C64" t="s">
         <v>12</v>
@@ -3637,30 +3867,30 @@
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F64" t="s">
         <v>14</v>
       </c>
       <c r="G64" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H64" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I64" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J64" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B65" t="s">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="C65" t="s">
         <v>12</v>
@@ -3669,30 +3899,30 @@
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F65" t="s">
         <v>14</v>
       </c>
       <c r="G65" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H65" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="I65" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J65" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>354</v>
       </c>
       <c r="C66" t="s">
         <v>12</v>
@@ -3701,30 +3931,30 @@
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F66" t="s">
         <v>14</v>
       </c>
       <c r="G66" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H66" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="I66" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="J66" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B67" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="C67" t="s">
         <v>12</v>
@@ -3733,30 +3963,30 @@
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F67" t="s">
         <v>14</v>
       </c>
       <c r="G67" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H67" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="I67" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="J67" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
@@ -3765,30 +3995,30 @@
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F68" t="s">
         <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H68" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="I68" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="J68" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="C69" t="s">
         <v>12</v>
@@ -3797,30 +4027,30 @@
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F69" t="s">
         <v>14</v>
       </c>
       <c r="G69" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H69" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I69" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J69" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B70" t="s">
-        <v>181</v>
+        <v>375</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
@@ -3829,30 +4059,30 @@
         <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F70" t="s">
         <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H70" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="I70" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J70" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>232</v>
       </c>
       <c r="C71" t="s">
         <v>12</v>
@@ -3861,30 +4091,30 @@
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="F71" t="s">
         <v>14</v>
       </c>
       <c r="G71" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H71" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="I71" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="J71" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B72" t="s">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="C72" t="s">
         <v>12</v>
@@ -3893,30 +4123,30 @@
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F72" t="s">
         <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H72" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="I72" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="J72" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B73" t="s">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="C73" t="s">
         <v>12</v>
@@ -3925,30 +4155,30 @@
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="F73" t="s">
         <v>14</v>
       </c>
       <c r="G73" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H73" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="I73" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="J73" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B74" t="s">
-        <v>78</v>
+        <v>308</v>
       </c>
       <c r="C74" t="s">
         <v>12</v>
@@ -3957,30 +4187,30 @@
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F74" t="s">
         <v>14</v>
       </c>
       <c r="G74" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H74" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="I74" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="J74" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B75" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="C75" t="s">
         <v>12</v>
@@ -3989,22 +4219,438 @@
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="F75" t="s">
         <v>14</v>
       </c>
       <c r="G75" t="s">
+        <v>74</v>
+      </c>
+      <c r="H75" t="s">
+        <v>402</v>
+      </c>
+      <c r="I75" t="s">
+        <v>403</v>
+      </c>
+      <c r="J75" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>405</v>
+      </c>
+      <c r="B76" t="s">
+        <v>109</v>
+      </c>
+      <c r="C76" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" t="s">
+        <v>406</v>
+      </c>
+      <c r="F76" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" t="s">
+        <v>74</v>
+      </c>
+      <c r="H76" t="s">
+        <v>407</v>
+      </c>
+      <c r="I76" t="s">
+        <v>408</v>
+      </c>
+      <c r="J76" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>410</v>
+      </c>
+      <c r="B77" t="s">
+        <v>79</v>
+      </c>
+      <c r="C77" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77" t="s">
+        <v>411</v>
+      </c>
+      <c r="F77" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" t="s">
+        <v>74</v>
+      </c>
+      <c r="H77" t="s">
+        <v>412</v>
+      </c>
+      <c r="I77" t="s">
+        <v>413</v>
+      </c>
+      <c r="J77" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>415</v>
+      </c>
+      <c r="B78" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" t="s">
+        <v>416</v>
+      </c>
+      <c r="F78" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" t="s">
+        <v>74</v>
+      </c>
+      <c r="H78" t="s">
+        <v>417</v>
+      </c>
+      <c r="I78" t="s">
+        <v>418</v>
+      </c>
+      <c r="J78" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>420</v>
+      </c>
+      <c r="B79" t="s">
+        <v>232</v>
+      </c>
+      <c r="C79" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79" t="s">
+        <v>421</v>
+      </c>
+      <c r="F79" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" t="s">
+        <v>74</v>
+      </c>
+      <c r="H79" t="s">
+        <v>422</v>
+      </c>
+      <c r="I79" t="s">
+        <v>423</v>
+      </c>
+      <c r="J79" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>425</v>
+      </c>
+      <c r="B80" t="s">
+        <v>109</v>
+      </c>
+      <c r="C80" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80" t="s">
+        <v>426</v>
+      </c>
+      <c r="F80" t="s">
+        <v>14</v>
+      </c>
+      <c r="G80" t="s">
+        <v>74</v>
+      </c>
+      <c r="H80" t="s">
+        <v>427</v>
+      </c>
+      <c r="I80" t="s">
+        <v>428</v>
+      </c>
+      <c r="J80" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>430</v>
+      </c>
+      <c r="B81" t="s">
+        <v>232</v>
+      </c>
+      <c r="C81" t="s">
+        <v>12</v>
+      </c>
+      <c r="D81" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" t="s">
+        <v>431</v>
+      </c>
+      <c r="F81" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" t="s">
+        <v>74</v>
+      </c>
+      <c r="H81" t="s">
+        <v>432</v>
+      </c>
+      <c r="I81" t="s">
+        <v>433</v>
+      </c>
+      <c r="J81" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>435</v>
+      </c>
+      <c r="B82" t="s">
+        <v>232</v>
+      </c>
+      <c r="C82" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82" t="s">
+        <v>436</v>
+      </c>
+      <c r="F82" t="s">
+        <v>14</v>
+      </c>
+      <c r="G82" t="s">
+        <v>74</v>
+      </c>
+      <c r="H82" t="s">
+        <v>437</v>
+      </c>
+      <c r="I82" t="s">
+        <v>438</v>
+      </c>
+      <c r="J82" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>440</v>
+      </c>
+      <c r="B83" t="s">
+        <v>130</v>
+      </c>
+      <c r="C83" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" t="s">
+        <v>441</v>
+      </c>
+      <c r="F83" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" t="s">
+        <v>74</v>
+      </c>
+      <c r="H83" t="s">
+        <v>442</v>
+      </c>
+      <c r="I83" t="s">
+        <v>443</v>
+      </c>
+      <c r="J83" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>445</v>
+      </c>
+      <c r="B84" t="s">
+        <v>85</v>
+      </c>
+      <c r="C84" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" t="s">
+        <v>446</v>
+      </c>
+      <c r="F84" t="s">
+        <v>14</v>
+      </c>
+      <c r="G84" t="s">
+        <v>74</v>
+      </c>
+      <c r="H84" t="s">
+        <v>447</v>
+      </c>
+      <c r="I84" t="s">
+        <v>448</v>
+      </c>
+      <c r="J84" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>450</v>
+      </c>
+      <c r="B85" t="s">
+        <v>451</v>
+      </c>
+      <c r="C85" t="s">
+        <v>12</v>
+      </c>
+      <c r="D85" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" t="s">
+        <v>452</v>
+      </c>
+      <c r="F85" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" t="s">
         <v>22</v>
       </c>
-      <c r="H75" t="s">
-        <v>396</v>
-      </c>
-      <c r="I75" t="s">
-        <v>397</v>
-      </c>
-      <c r="J75" t="s">
-        <v>398</v>
+      <c r="H85" t="s">
+        <v>453</v>
+      </c>
+      <c r="I85" t="s">
+        <v>454</v>
+      </c>
+      <c r="J85" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>456</v>
+      </c>
+      <c r="B86" t="s">
+        <v>457</v>
+      </c>
+      <c r="C86" t="s">
+        <v>12</v>
+      </c>
+      <c r="D86" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" t="s">
+        <v>458</v>
+      </c>
+      <c r="F86" t="s">
+        <v>14</v>
+      </c>
+      <c r="G86" t="s">
+        <v>22</v>
+      </c>
+      <c r="H86" t="s">
+        <v>459</v>
+      </c>
+      <c r="I86" t="s">
+        <v>460</v>
+      </c>
+      <c r="J86" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>462</v>
+      </c>
+      <c r="B87" t="s">
+        <v>463</v>
+      </c>
+      <c r="C87" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" t="s">
+        <v>464</v>
+      </c>
+      <c r="F87" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" t="s">
+        <v>465</v>
+      </c>
+      <c r="H87" t="s">
+        <v>466</v>
+      </c>
+      <c r="I87" t="s">
+        <v>467</v>
+      </c>
+      <c r="J87" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>469</v>
+      </c>
+      <c r="B88" t="s">
+        <v>470</v>
+      </c>
+      <c r="C88" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" t="s">
+        <v>471</v>
+      </c>
+      <c r="F88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G88" t="s">
+        <v>22</v>
+      </c>
+      <c r="H88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I88" t="s">
+        <v>473</v>
+      </c>
+      <c r="J88" t="s">
+        <v>474</v>
       </c>
     </row>
   </sheetData>
